--- a/parts-lists/DAZ_wheel_AliExpress_cart_list_AUD.xlsx
+++ b/parts-lists/DAZ_wheel_AliExpress_cart_list_AUD.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="137">
   <si>
     <t xml:space="preserve">DAZ V2 steering wheel – AliExpress cart list (AUD)</t>
   </si>
@@ -175,19 +175,16 @@
     <t xml:space="preserve">XT60 plugs (male + female)</t>
   </si>
   <si>
-    <t xml:space="preserve">Smallest pack offered (you need 1 pair)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMASS XT60 listing</t>
+    <t xml:space="preserve">10 pcs = 5 pairs (smallest pack on this listing; you need 1 pair)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT60H listing</t>
   </si>
   <si>
     <t xml:space="preserve">Search: XT60 pair</t>
   </si>
   <si>
-    <t xml:space="preserve">Not auto-checked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't buy a 10-pair pack. Jaycar PT4458 is ≈ $5 a pair if you want it today.</t>
+    <t xml:space="preserve">Don't buy bigger packs. Or get one pair from Jaycar (PT4458, ≈ $5) and skip this line.</t>
   </si>
   <si>
     <t xml:space="preserve">Motor axle clamp</t>
@@ -265,9 +262,6 @@
     <t xml:space="preserve">Search: M5x20</t>
   </si>
   <si>
-    <t xml:space="preserve">Link OK – not auto-checked</t>
-  </si>
-  <si>
     <t xml:space="preserve">M5 × 25 · smallest quantity</t>
   </si>
   <si>
@@ -304,13 +298,16 @@
     <t xml:space="preserve">Self-tapping screws</t>
   </si>
   <si>
-    <t xml:space="preserve">M3 × 12 · smallest quantity</t>
+    <t xml:space="preserve">ST2.9 (≈ M3) × 13 mm · smallest quantity (DAZ: M3 × 12)</t>
   </si>
   <si>
     <t xml:space="preserve">Search: M3x12</t>
   </si>
   <si>
-    <t xml:space="preserve">M2.5 × 6 · smallest quantity</t>
+    <t xml:space="preserve">Self-tappers are sold in ST sizes; the nearest length is fine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST2.2 (≈ M2.5) × 6.5 mm · smallest quantity (DAZ: M2.5 × 6)</t>
   </si>
   <si>
     <t xml:space="preserve">Search: M2.5x6</t>
@@ -436,7 +433,7 @@
     <t xml:space="preserve">• Target prices: estimates in AUD incl. 10% GST from DAZ's link prices (mostly May 2025) and a 3 Oct 2026 price search on AliExpress's US store, whose prices include US import tariffs. Australian prices are usually a little lower. Edit the blue cells if you find better prices.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Already have the hoverboard motor, so it isn't in the cart. Same total as the wheel parts list (≈ $191).</t>
+    <t xml:space="preserve">• Already have the hoverboard motor, so it isn't in the cart. Same total as the wheel parts list (≈ $193).</t>
   </si>
 </sst>
 </file>
@@ -627,7 +624,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -700,8 +697,8 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -714,10 +711,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1043,7 +1036,7 @@
       </c>
       <c r="G3" s="4" t="n">
         <f aca="false">G40</f>
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,11 +1405,11 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="13" t="n">
         <f aca="false">E15*F15</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="13" t="str">
@@ -1430,10 +1423,10 @@
         <v>52</v>
       </c>
       <c r="L15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1442,10 +1435,10 @@
         <v>9</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>1</v>
@@ -1466,13 +1459,13 @@
         <v>21</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L16" s="16" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1481,10 +1474,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>59</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="E17" s="11" t="n">
         <v>1</v>
@@ -1505,13 +1498,13 @@
         <v>21</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>23</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1520,10 +1513,10 @@
         <v>11</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>64</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>1</v>
@@ -1541,16 +1534,16 @@
         <v/>
       </c>
       <c r="J18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K18" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="L18" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1559,10 +1552,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>69</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>1</v>
@@ -1583,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>23</v>
@@ -1596,10 +1589,10 @@
         <v>13</v>
       </c>
       <c r="C20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>1</v>
@@ -1617,21 +1610,21 @@
         <v/>
       </c>
       <c r="J20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="L20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1646,16 +1639,16 @@
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8"/>
       <c r="B23" s="9" t="n">
         <v>14</v>
       </c>
       <c r="C23" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>1</v>
@@ -1676,23 +1669,23 @@
         <v>21</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M23" s="10"/>
     </row>
-    <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8"/>
       <c r="B24" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>1</v>
@@ -1713,23 +1706,23 @@
         <v>21</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M24" s="10"/>
     </row>
-    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8"/>
       <c r="B25" s="9" t="n">
         <v>16</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>1</v>
@@ -1750,23 +1743,23 @@
         <v>21</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M25" s="10"/>
     </row>
-    <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="n">
         <v>17</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>1</v>
@@ -1787,23 +1780,23 @@
         <v>21</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M26" s="10"/>
     </row>
-    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8"/>
       <c r="B27" s="9" t="n">
         <v>18</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
@@ -1824,23 +1817,23 @@
         <v>21</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M27" s="10"/>
     </row>
-    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E28" s="11" t="n">
         <v>1</v>
@@ -1861,10 +1854,10 @@
         <v>21</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M28" s="10"/>
     </row>
@@ -1874,10 +1867,10 @@
         <v>20</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
@@ -1898,12 +1891,14 @@
         <v>21</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="M29" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8"/>
@@ -1911,10 +1906,10 @@
         <v>21</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>1</v>
@@ -1935,23 +1930,23 @@
         <v>21</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M30" s="10"/>
     </row>
-    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8"/>
       <c r="B31" s="9" t="n">
         <v>22</v>
       </c>
       <c r="C31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>1</v>
@@ -1972,23 +1967,23 @@
         <v>21</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8"/>
       <c r="B32" s="9" t="n">
         <v>23</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>1</v>
@@ -2009,16 +2004,16 @@
         <v>21</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="M32" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -2039,10 +2034,10 @@
         <v>24</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="E35" s="11" t="n">
         <v>1</v>
@@ -2060,16 +2055,16 @@
         <v/>
       </c>
       <c r="J35" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="K35" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="K35" s="15" t="s">
+      <c r="L35" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="L35" s="16" t="s">
+      <c r="M35" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2078,10 +2073,10 @@
         <v>25</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>1</v>
@@ -2099,20 +2094,20 @@
         <v/>
       </c>
       <c r="J36" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K36" s="17"/>
       <c r="L36" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M36" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C38" s="3" t="s">
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C38" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>113</v>
       </c>
       <c r="G38" s="19" t="n">
         <v>0</v>
@@ -2122,169 +2117,169 @@
         <f aca="false">IF(H38="","",H38-G38)</f>
         <v/>
       </c>
-      <c r="M38" s="22" t="s">
+      <c r="M38" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23" t="s">
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="23" t="n">
+        <f aca="false">SUM(G8:G38)</f>
+        <v>193</v>
+      </c>
+      <c r="H40" s="23" t="str">
+        <f aca="false">IF(COUNT(H8:H38)=0,"",SUM(H8:H38))</f>
+        <v/>
+      </c>
+      <c r="I40" s="23" t="str">
+        <f aca="false">IF(COUNT(H8:H38)=0,"",SUM(I8:I38))</f>
+        <v/>
+      </c>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="24" t="n">
-        <f aca="false">SUM(G8:G38)</f>
-        <v>191</v>
-      </c>
-      <c r="H40" s="24" t="str">
-        <f aca="false">IF(COUNT(H8:H38)=0,"",SUM(H8:H38))</f>
-        <v/>
-      </c>
-      <c r="I40" s="24" t="str">
-        <f aca="false">IF(COUNT(H8:H38)=0,"",SUM(I8:I38))</f>
-        <v/>
-      </c>
-      <c r="J40" s="23"/>
-      <c r="K40" s="23"/>
-      <c r="L40" s="23"/>
-      <c r="M40" s="23"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
     </row>
     <row r="43" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="M43" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C44" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="M44" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="M44" s="10" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C45" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D45" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="M45" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C46" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="M46" s="10" t="s">
         <v>127</v>
-      </c>
-      <c r="M46" s="10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C47" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="M47" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C48" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="M48" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="M48" s="10" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="26" t="s">
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="26" t="s">
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2315,7 +2310,7 @@
     <hyperlink ref="K13" r:id="rId12" display="Search: GT2 idler 20T 5 mm"/>
     <hyperlink ref="J14" r:id="rId13" display="24 V adapter listing"/>
     <hyperlink ref="K14" r:id="rId14" display="Search: 24V 10A AU plug"/>
-    <hyperlink ref="J15" r:id="rId15" display="AMASS XT60 listing"/>
+    <hyperlink ref="J15" r:id="rId15" display="XT60H listing"/>
     <hyperlink ref="K15" r:id="rId16" display="Search: XT60 pair"/>
     <hyperlink ref="J16" r:id="rId17" display="DAZ's listing"/>
     <hyperlink ref="K16" r:id="rId18" display="Search: 16 mm cross clamp"/>
